--- a/tests/Roster.Tests/Fixtures/members-100.xlsx
+++ b/tests/Roster.Tests/Fixtures/members-100.xlsx
@@ -526,7 +526,7 @@
     <t xml:space="preserve">thaddeus.sample@example.invalid</t>
   </si>
   <si>
-    <t xml:space="preserve">Aaron Example</t>
+    <t xml:space="preserve">Aaron Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">6/14</t>
@@ -535,10 +535,10 @@
     <t xml:space="preserve">555-0141</t>
   </si>
   <si>
-    <t xml:space="preserve">aaron.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bertram Example</t>
+    <t xml:space="preserve">aaron.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bertram Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">7/15</t>
@@ -547,10 +547,10 @@
     <t xml:space="preserve">555-0142</t>
   </si>
   <si>
-    <t xml:space="preserve">bertram.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyrus Example</t>
+    <t xml:space="preserve">bertram.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyrus Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">8/16</t>
@@ -559,10 +559,10 @@
     <t xml:space="preserve">555-0143</t>
   </si>
   <si>
-    <t xml:space="preserve">cyrus.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorian Example</t>
+    <t xml:space="preserve">cyrus.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorian Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">9/17</t>
@@ -571,10 +571,10 @@
     <t xml:space="preserve">555-0144</t>
   </si>
   <si>
-    <t xml:space="preserve">dorian.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ephraim Example</t>
+    <t xml:space="preserve">dorian.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ephraim Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">10/18</t>
@@ -583,10 +583,10 @@
     <t xml:space="preserve">555-0145</t>
   </si>
   <si>
-    <t xml:space="preserve">ephraim.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fenwick Example</t>
+    <t xml:space="preserve">ephraim.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenwick Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">11/19</t>
@@ -595,10 +595,10 @@
     <t xml:space="preserve">555-0146</t>
   </si>
   <si>
-    <t xml:space="preserve">fenwick.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gideon Example</t>
+    <t xml:space="preserve">fenwick.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gideon Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">12/20</t>
@@ -607,10 +607,10 @@
     <t xml:space="preserve">555-0147</t>
   </si>
   <si>
-    <t xml:space="preserve">gideon.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horace Example</t>
+    <t xml:space="preserve">gideon.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horace Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">1/21</t>
@@ -619,10 +619,10 @@
     <t xml:space="preserve">555-0148</t>
   </si>
   <si>
-    <t xml:space="preserve">horace.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignatius Example</t>
+    <t xml:space="preserve">horace.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignatius Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">2/22</t>
@@ -631,10 +631,10 @@
     <t xml:space="preserve">555-0149</t>
   </si>
   <si>
-    <t xml:space="preserve">ignatius.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasper Example</t>
+    <t xml:space="preserve">ignatius.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasper Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">3/23</t>
@@ -643,10 +643,10 @@
     <t xml:space="preserve">555-0150</t>
   </si>
   <si>
-    <t xml:space="preserve">jasper.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kendrick Example</t>
+    <t xml:space="preserve">jasper.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kendrick Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">4/24</t>
@@ -655,10 +655,10 @@
     <t xml:space="preserve">555-0151</t>
   </si>
   <si>
-    <t xml:space="preserve">kendrick.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lysander Example</t>
+    <t xml:space="preserve">kendrick.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lysander Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">5/25</t>
@@ -667,10 +667,10 @@
     <t xml:space="preserve">555-0152</t>
   </si>
   <si>
-    <t xml:space="preserve">lysander.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortimer Example</t>
+    <t xml:space="preserve">lysander.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortimer Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">6/26</t>
@@ -679,10 +679,10 @@
     <t xml:space="preserve">555-0153</t>
   </si>
   <si>
-    <t xml:space="preserve">mortimer.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathaniel Example</t>
+    <t xml:space="preserve">mortimer.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathaniel Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">7/27</t>
@@ -691,10 +691,10 @@
     <t xml:space="preserve">555-0154</t>
   </si>
   <si>
-    <t xml:space="preserve">nathaniel.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octavius Example</t>
+    <t xml:space="preserve">nathaniel.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octavius Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">8/28</t>
@@ -703,10 +703,10 @@
     <t xml:space="preserve">555-0155</t>
   </si>
   <si>
-    <t xml:space="preserve">octavius.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percival Example</t>
+    <t xml:space="preserve">octavius.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percival Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">9/1</t>
@@ -715,10 +715,10 @@
     <t xml:space="preserve">555-0156</t>
   </si>
   <si>
-    <t xml:space="preserve">percival.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quentin Example</t>
+    <t xml:space="preserve">percival.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">10/2</t>
@@ -727,10 +727,10 @@
     <t xml:space="preserve">555-0157</t>
   </si>
   <si>
-    <t xml:space="preserve">quentin.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rupert Example</t>
+    <t xml:space="preserve">quentin.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupert Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">11/3</t>
@@ -739,10 +739,10 @@
     <t xml:space="preserve">555-0158</t>
   </si>
   <si>
-    <t xml:space="preserve">rupert.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silas Example</t>
+    <t xml:space="preserve">rupert.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silas Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">12/4</t>
@@ -751,10 +751,10 @@
     <t xml:space="preserve">555-0159</t>
   </si>
   <si>
-    <t xml:space="preserve">silas.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thaddeus Example</t>
+    <t xml:space="preserve">silas.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thaddeus Fictitious</t>
   </si>
   <si>
     <t xml:space="preserve">1/5</t>
@@ -763,10 +763,10 @@
     <t xml:space="preserve">555-0160</t>
   </si>
   <si>
-    <t xml:space="preserve">thaddeus.example@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Fictitious</t>
+    <t xml:space="preserve">thaddeus.fictitious@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">2/6</t>
@@ -775,10 +775,10 @@
     <t xml:space="preserve">555-0161</t>
   </si>
   <si>
-    <t xml:space="preserve">aaron.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bertram Fictitious</t>
+    <t xml:space="preserve">aaron.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bertram Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">3/7</t>
@@ -787,10 +787,10 @@
     <t xml:space="preserve">555-0162</t>
   </si>
   <si>
-    <t xml:space="preserve">bertram.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyrus Fictitious</t>
+    <t xml:space="preserve">bertram.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyrus Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">4/8</t>
@@ -799,10 +799,10 @@
     <t xml:space="preserve">555-0163</t>
   </si>
   <si>
-    <t xml:space="preserve">cyrus.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorian Fictitious</t>
+    <t xml:space="preserve">cyrus.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorian Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">5/9</t>
@@ -811,10 +811,10 @@
     <t xml:space="preserve">555-0164</t>
   </si>
   <si>
-    <t xml:space="preserve">dorian.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ephraim Fictitious</t>
+    <t xml:space="preserve">dorian.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ephraim Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">6/10</t>
@@ -823,10 +823,10 @@
     <t xml:space="preserve">555-0165</t>
   </si>
   <si>
-    <t xml:space="preserve">ephraim.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fenwick Fictitious</t>
+    <t xml:space="preserve">ephraim.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenwick Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">7/11</t>
@@ -835,10 +835,10 @@
     <t xml:space="preserve">555-0166</t>
   </si>
   <si>
-    <t xml:space="preserve">fenwick.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gideon Fictitious</t>
+    <t xml:space="preserve">fenwick.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gideon Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">8/12</t>
@@ -847,10 +847,10 @@
     <t xml:space="preserve">555-0167</t>
   </si>
   <si>
-    <t xml:space="preserve">gideon.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horace Fictitious</t>
+    <t xml:space="preserve">gideon.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horace Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">9/13</t>
@@ -859,10 +859,10 @@
     <t xml:space="preserve">555-0168</t>
   </si>
   <si>
-    <t xml:space="preserve">horace.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignatius Fictitious</t>
+    <t xml:space="preserve">horace.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignatius Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">10/14</t>
@@ -871,10 +871,10 @@
     <t xml:space="preserve">555-0169</t>
   </si>
   <si>
-    <t xml:space="preserve">ignatius.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasper Fictitious</t>
+    <t xml:space="preserve">ignatius.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasper Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">11/15</t>
@@ -883,10 +883,10 @@
     <t xml:space="preserve">555-0170</t>
   </si>
   <si>
-    <t xml:space="preserve">jasper.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kendrick Fictitious</t>
+    <t xml:space="preserve">jasper.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kendrick Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">12/16</t>
@@ -895,10 +895,10 @@
     <t xml:space="preserve">555-0171</t>
   </si>
   <si>
-    <t xml:space="preserve">kendrick.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lysander Fictitious</t>
+    <t xml:space="preserve">kendrick.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lysander Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">1/17</t>
@@ -907,10 +907,10 @@
     <t xml:space="preserve">555-0172</t>
   </si>
   <si>
-    <t xml:space="preserve">lysander.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortimer Fictitious</t>
+    <t xml:space="preserve">lysander.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortimer Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">2/18</t>
@@ -919,10 +919,10 @@
     <t xml:space="preserve">555-0173</t>
   </si>
   <si>
-    <t xml:space="preserve">mortimer.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathaniel Fictitious</t>
+    <t xml:space="preserve">mortimer.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathaniel Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">3/19</t>
@@ -931,10 +931,10 @@
     <t xml:space="preserve">555-0174</t>
   </si>
   <si>
-    <t xml:space="preserve">nathaniel.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octavius Fictitious</t>
+    <t xml:space="preserve">nathaniel.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octavius Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">4/20</t>
@@ -943,10 +943,10 @@
     <t xml:space="preserve">555-0175</t>
   </si>
   <si>
-    <t xml:space="preserve">octavius.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percival Fictitious</t>
+    <t xml:space="preserve">octavius.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percival Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">5/21</t>
@@ -955,10 +955,10 @@
     <t xml:space="preserve">555-0176</t>
   </si>
   <si>
-    <t xml:space="preserve">percival.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quentin Fictitious</t>
+    <t xml:space="preserve">percival.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">6/22</t>
@@ -967,10 +967,10 @@
     <t xml:space="preserve">555-0177</t>
   </si>
   <si>
-    <t xml:space="preserve">quentin.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rupert Fictitious</t>
+    <t xml:space="preserve">quentin.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupert Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">7/23</t>
@@ -979,10 +979,10 @@
     <t xml:space="preserve">555-0178</t>
   </si>
   <si>
-    <t xml:space="preserve">rupert.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silas Fictitious</t>
+    <t xml:space="preserve">rupert.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silas Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">8/24</t>
@@ -991,10 +991,10 @@
     <t xml:space="preserve">555-0179</t>
   </si>
   <si>
-    <t xml:space="preserve">silas.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thaddeus Fictitious</t>
+    <t xml:space="preserve">silas.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thaddeus Testcase</t>
   </si>
   <si>
     <t xml:space="preserve">9/25</t>
@@ -1003,10 +1003,10 @@
     <t xml:space="preserve">555-0180</t>
   </si>
   <si>
-    <t xml:space="preserve">thaddeus.fictitious@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Testcase</t>
+    <t xml:space="preserve">thaddeus.testcase@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">10/26</t>
@@ -1015,10 +1015,10 @@
     <t xml:space="preserve">555-0181</t>
   </si>
   <si>
-    <t xml:space="preserve">aaron.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bertram Testcase</t>
+    <t xml:space="preserve">aaron.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bertram Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">11/27</t>
@@ -1027,10 +1027,10 @@
     <t xml:space="preserve">555-0182</t>
   </si>
   <si>
-    <t xml:space="preserve">bertram.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyrus Testcase</t>
+    <t xml:space="preserve">bertram.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyrus Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">12/28</t>
@@ -1039,10 +1039,10 @@
     <t xml:space="preserve">555-0183</t>
   </si>
   <si>
-    <t xml:space="preserve">cyrus.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorian Testcase</t>
+    <t xml:space="preserve">cyrus.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorian Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">1/1</t>
@@ -1051,151 +1051,151 @@
     <t xml:space="preserve">555-0184</t>
   </si>
   <si>
-    <t xml:space="preserve">dorian.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ephraim Testcase</t>
+    <t xml:space="preserve">dorian.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ephraim Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0185</t>
   </si>
   <si>
-    <t xml:space="preserve">ephraim.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fenwick Testcase</t>
+    <t xml:space="preserve">ephraim.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenwick Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0186</t>
   </si>
   <si>
-    <t xml:space="preserve">fenwick.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gideon Testcase</t>
+    <t xml:space="preserve">fenwick.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gideon Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0187</t>
   </si>
   <si>
-    <t xml:space="preserve">gideon.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horace Testcase</t>
+    <t xml:space="preserve">gideon.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horace Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0188</t>
   </si>
   <si>
-    <t xml:space="preserve">horace.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignatius Testcase</t>
+    <t xml:space="preserve">horace.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignatius Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0189</t>
   </si>
   <si>
-    <t xml:space="preserve">ignatius.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasper Testcase</t>
+    <t xml:space="preserve">ignatius.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasper Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0190</t>
   </si>
   <si>
-    <t xml:space="preserve">jasper.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kendrick Testcase</t>
+    <t xml:space="preserve">jasper.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kendrick Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0191</t>
   </si>
   <si>
-    <t xml:space="preserve">kendrick.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lysander Testcase</t>
+    <t xml:space="preserve">kendrick.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lysander Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0192</t>
   </si>
   <si>
-    <t xml:space="preserve">lysander.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortimer Testcase</t>
+    <t xml:space="preserve">lysander.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortimer Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0193</t>
   </si>
   <si>
-    <t xml:space="preserve">mortimer.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathaniel Testcase</t>
+    <t xml:space="preserve">mortimer.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathaniel Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0194</t>
   </si>
   <si>
-    <t xml:space="preserve">nathaniel.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octavius Testcase</t>
+    <t xml:space="preserve">nathaniel.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octavius Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0195</t>
   </si>
   <si>
-    <t xml:space="preserve">octavius.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percival Testcase</t>
+    <t xml:space="preserve">octavius.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percival Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0196</t>
   </si>
   <si>
-    <t xml:space="preserve">percival.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quentin Testcase</t>
+    <t xml:space="preserve">percival.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0197</t>
   </si>
   <si>
-    <t xml:space="preserve">quentin.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rupert Testcase</t>
+    <t xml:space="preserve">quentin.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupert Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0198</t>
   </si>
   <si>
-    <t xml:space="preserve">rupert.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silas Testcase</t>
+    <t xml:space="preserve">rupert.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silas Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0199</t>
   </si>
   <si>
-    <t xml:space="preserve">silas.testcase@example.invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thaddeus Testcase</t>
+    <t xml:space="preserve">silas.anonymous@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thaddeus Anonymous</t>
   </si>
   <si>
     <t xml:space="preserve">555-0200</t>
   </si>
   <si>
-    <t xml:space="preserve">thaddeus.testcase@example.invalid</t>
+    <t xml:space="preserve">thaddeus.anonymous@example.invalid</t>
   </si>
 </sst>
 </file>
